--- a/reports/2026-09_月次実績報告/excel/【営業会議資料】令和8年9月実績.xlsx
+++ b/reports/2026-09_月次実績報告/excel/【営業会議資料】令和8年9月実績.xlsx
@@ -14423,7 +14423,7 @@
         <v>121650</v>
       </c>
       <c r="I7" s="260" t="n">
-        <v>113384.79</v>
+        <v>113385.265</v>
       </c>
       <c r="J7" s="261">
         <f>I7-H7</f>
@@ -14447,7 +14447,7 @@
         <v>29660</v>
       </c>
       <c r="P7" s="260" t="n">
-        <v>28930.676</v>
+        <v>28929.7936</v>
       </c>
       <c r="Q7" s="261">
         <f>P7-O7</f>
@@ -14680,7 +14680,7 @@
         <v>55690</v>
       </c>
       <c r="I10" s="285" t="n">
-        <v>63348.432</v>
+        <v>63348.641</v>
       </c>
       <c r="J10" s="286">
         <f>I10-H10</f>
@@ -14704,7 +14704,7 @@
         <v>14590</v>
       </c>
       <c r="P10" s="285" t="n">
-        <v>17677.109</v>
+        <v>17677.993</v>
       </c>
       <c r="Q10" s="286">
         <f>P10-O10</f>
@@ -15194,7 +15194,7 @@
         <v>116640</v>
       </c>
       <c r="I16" s="285" t="n">
-        <v>118738.66</v>
+        <v>118738.492</v>
       </c>
       <c r="J16" s="286">
         <f>I16-H16</f>
@@ -15218,7 +15218,7 @@
         <v>27690</v>
       </c>
       <c r="P16" s="285" t="n">
-        <v>32607.6254</v>
+        <v>32607.1698</v>
       </c>
       <c r="Q16" s="286">
         <f>P16-O16</f>
@@ -18564,7 +18564,7 @@
         <v>61330</v>
       </c>
       <c r="I56" s="260" t="n">
-        <v>67884.22099999999</v>
+        <v>67867.538</v>
       </c>
       <c r="J56" s="261">
         <f>I56-H56</f>
@@ -18588,7 +18588,7 @@
         <v>18730</v>
       </c>
       <c r="P56" s="260" t="n">
-        <v>22219.825</v>
+        <v>22214.468</v>
       </c>
       <c r="Q56" s="261">
         <f>P56-O56</f>
@@ -18821,7 +18821,7 @@
         <v>59500</v>
       </c>
       <c r="I59" s="285" t="n">
-        <v>76330.50100000002</v>
+        <v>75818.451</v>
       </c>
       <c r="J59" s="286">
         <f>I59-H59</f>
@@ -18845,7 +18845,7 @@
         <v>14030</v>
       </c>
       <c r="P59" s="285" t="n">
-        <v>17439.6797</v>
+        <v>17472.5636</v>
       </c>
       <c r="Q59" s="286">
         <f>P59-O59</f>
@@ -19019,7 +19019,7 @@
         <v>390</v>
       </c>
       <c r="P61" s="277" t="n">
-        <v>882.348</v>
+        <v>880.0279999999999</v>
       </c>
       <c r="Q61" s="269">
         <f>P61-O61</f>
@@ -19078,7 +19078,7 @@
         <v>55670</v>
       </c>
       <c r="I62" s="277" t="n">
-        <v>61366.225</v>
+        <v>61935.70800000001</v>
       </c>
       <c r="J62" s="269">
         <f>I62-H62</f>
@@ -19102,7 +19102,7 @@
         <v>12820</v>
       </c>
       <c r="P62" s="277" t="n">
-        <v>15758.876</v>
+        <v>15910.523</v>
       </c>
       <c r="Q62" s="269">
         <f>P62-O62</f>
@@ -20713,7 +20713,7 @@
         <v>37080</v>
       </c>
       <c r="I82" s="285" t="n">
-        <v>34660.171</v>
+        <v>34660.29400000001</v>
       </c>
       <c r="J82" s="286">
         <f>I82-H82</f>
@@ -21388,7 +21388,7 @@
         <v>37740</v>
       </c>
       <c r="I91" s="285" t="n">
-        <v>31084.131</v>
+        <v>31083.81</v>
       </c>
       <c r="J91" s="286">
         <f>I91-H91</f>
@@ -21412,7 +21412,7 @@
         <v>4755</v>
       </c>
       <c r="P91" s="285" t="n">
-        <v>3920.279</v>
+        <v>3812.288</v>
       </c>
       <c r="Q91" s="286">
         <f>P91-O91</f>
@@ -22705,7 +22705,7 @@
         <v>72580</v>
       </c>
       <c r="I106" s="285" t="n">
-        <v>79140.486</v>
+        <v>79140.622</v>
       </c>
       <c r="J106" s="286">
         <f>I106-H106</f>
@@ -22729,7 +22729,7 @@
         <v>15980</v>
       </c>
       <c r="P106" s="285" t="n">
-        <v>16498.657</v>
+        <v>16498.33</v>
       </c>
       <c r="Q106" s="286">
         <f>P106-O106</f>
@@ -25221,7 +25221,7 @@
         <v>239050</v>
       </c>
       <c r="I135" s="348" t="n">
-        <v>284711.48</v>
+        <v>284507.551</v>
       </c>
       <c r="J135" s="349">
         <f>I135-H135</f>
@@ -25245,7 +25245,7 @@
         <v>71970</v>
       </c>
       <c r="P135" s="348" t="n">
-        <v>83672.12299999999</v>
+        <v>83459.16899999999</v>
       </c>
       <c r="Q135" s="349">
         <f>P135-O135</f>
@@ -25395,7 +25395,7 @@
         <v>46940</v>
       </c>
       <c r="I137" s="361" t="n">
-        <v>43682.933</v>
+        <v>43682.707</v>
       </c>
       <c r="J137" s="332">
         <f>I137-H137</f>
@@ -25419,7 +25419,7 @@
         <v>27350</v>
       </c>
       <c r="P137" s="361" t="n">
-        <v>26356.515</v>
+        <v>26356.906</v>
       </c>
       <c r="Q137" s="332">
         <f>P137-O137</f>
@@ -25478,7 +25478,7 @@
         <v>840</v>
       </c>
       <c r="I138" s="363" t="n">
-        <v>1443.13</v>
+        <v>1443.3</v>
       </c>
       <c r="J138" s="339">
         <f>I138-H138</f>
@@ -25502,7 +25502,7 @@
         <v>180</v>
       </c>
       <c r="P138" s="363" t="n">
-        <v>300.39</v>
+        <v>300.9</v>
       </c>
       <c r="Q138" s="339">
         <f>P138-O138</f>

--- a/reports/2026-09_月次実績報告/excel/【営業会議資料】令和8年9月実績.xlsx
+++ b/reports/2026-09_月次実績報告/excel/【営業会議資料】令和8年9月実績.xlsx
@@ -2414,9 +2414,16 @@
   <cols>
     <col width="1.875" customWidth="1" style="236" min="1" max="4"/>
     <col width="19.5" customWidth="1" style="236" min="5" max="5"/>
-    <col width="8.5" customWidth="1" style="241" min="10" max="11"/>
-    <col width="9.375" customWidth="1" style="236" min="16" max="16"/>
-    <col width="8.5" customWidth="1" style="241" min="17" max="18"/>
+    <col width="14" customWidth="1" style="236" min="6" max="6"/>
+    <col width="14" customWidth="1" style="236" min="7" max="7"/>
+    <col width="14" customWidth="1" style="236" min="8" max="8"/>
+    <col width="14" customWidth="1" style="236" min="9" max="9"/>
+    <col width="12" customWidth="1" style="241" min="10" max="11"/>
+    <col width="14" customWidth="1" style="236" min="13" max="13"/>
+    <col width="14" customWidth="1" style="236" min="14" max="14"/>
+    <col width="14" customWidth="1" style="236" min="15" max="15"/>
+    <col width="14" customWidth="1" style="236" min="16" max="16"/>
+    <col width="12" customWidth="1" style="241" min="17" max="18"/>
     <col width="9.125" customWidth="1" style="236" min="20" max="23"/>
     <col width="9.375" customWidth="1" style="236" min="24" max="25"/>
   </cols>
@@ -14057,7 +14064,6 @@
         <v/>
       </c>
     </row>
-    <row r="142"/>
     <row r="143">
       <c r="A143" s="192" t="inlineStr">
         <is>
@@ -14170,10 +14176,16 @@
   <cols>
     <col width="1.875" customWidth="1" style="236" min="1" max="4"/>
     <col width="19.5" customWidth="1" style="236" min="5" max="5"/>
-    <col width="9.5" customWidth="1" style="236" min="8" max="9"/>
-    <col width="8.5" customWidth="1" style="241" min="10" max="11"/>
-    <col width="9.375" customWidth="1" style="236" min="16" max="16"/>
-    <col width="8.5" customWidth="1" style="241" min="17" max="18"/>
+    <col width="14" customWidth="1" style="236" min="6" max="6"/>
+    <col width="14" customWidth="1" style="236" min="7" max="7"/>
+    <col width="14" customWidth="1" style="236" min="8" max="9"/>
+    <col width="14" customWidth="1" style="236" min="9" max="9"/>
+    <col width="12" customWidth="1" style="241" min="10" max="11"/>
+    <col width="14" customWidth="1" style="236" min="13" max="13"/>
+    <col width="14" customWidth="1" style="236" min="14" max="14"/>
+    <col width="14" customWidth="1" style="236" min="15" max="15"/>
+    <col width="14" customWidth="1" style="236" min="16" max="16"/>
+    <col width="12" customWidth="1" style="241" min="17" max="18"/>
     <col width="9.125" customWidth="1" style="236" min="20" max="23"/>
     <col width="9.375" customWidth="1" style="236" min="24" max="25"/>
   </cols>
@@ -25814,7 +25826,6 @@
         <v/>
       </c>
     </row>
-    <row r="142"/>
     <row r="143">
       <c r="A143" s="192" t="inlineStr">
         <is>
